--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>103 filas de datos</t>
+          <t>102 filas de datos</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3854,7 +3854,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>Rb93cd3cbd9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pmid:37160359; doi:10.1136/bmjresp-2022-001360</t>
+          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3884,34 +3884,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC10173968</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>nfection Single- arm, open- labelled, safety and tolerability of intrabronchial and nebulis</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>metodos y analisis</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-arm, open-labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in children with cystic fibrosis </t>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rb93cd3cbd9</t>
+          <t>Rdfeb34f4ef</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
+          <t>doi:10.1016/j.eimc.2025.05.008</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rdfeb34f4ef</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.eimc.2025.05.008</t>
+          <t>doi:10.1093/ofid/ofad221</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3998,34 +3998,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>R607037aeaa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>doi:10.1093/ofid/ofad221</t>
+          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4055,34 +4055,34 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
+          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>R607037aeaa</t>
+          <t>R93e07521e9</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
+          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4112,34 +4112,34 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC7277081</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R93e07521e9</t>
+          <t>R4e80e5028d</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
+          <t>doi:10.15789/1563-0625-pti-2012</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PMC7277081</t>
+          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4179,24 +4179,24 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
+          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>R4e80e5028d</t>
+          <t>Rf41ce1f437</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>doi:10.15789/1563-0625-pti-2012</t>
+          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
+          <t>PMC10989018</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
+          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>resumen materiales y metodos</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rf41ce1f437</t>
+          <t>Re9fa49ae6d</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
+          <t>doi:10.1002/central/cn-02936419/full</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4283,34 +4283,34 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PMC10989018</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>resumen materiales y metodos</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Re9fa49ae6d</t>
+          <t>Rde30f4212d</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-02936419/full</t>
+          <t>doi:10.1089/phage.2020.0010</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4340,34 +4340,34 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC9041461</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
+          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rde30f4212d</t>
+          <t>Rbcb0bd26fd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>doi:10.1089/phage.2020.0010</t>
+          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4397,34 +4397,34 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PMC9041461</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
+          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rbcb0bd26fd</t>
+          <t>R188612f054</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
+          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4454,34 +4454,34 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC10034620</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R188612f054</t>
+          <t>R0b195c9d15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
+          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PMC10034620</t>
+          <t>PMC11442429</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4531,14 +4531,14 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R0b195c9d15</t>
+          <t>R72f673966a</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
+          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4568,34 +4568,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PMC11442429</t>
+          <t>PMC12786087</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
+          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R72f673966a</t>
+          <t>Rfc0fff7284</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
+          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PMC12786087</t>
+          <t>PMC12877064</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4635,24 +4635,24 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
+          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rfc0fff7284</t>
+          <t>Ra1f20b8500</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
+          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PMC12877064</t>
+          <t>PMC8422068</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
+          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ra1f20b8500</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
+          <t>doi:10.3390/antibiotics10060627</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PMC8422068</t>
+          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4749,24 +4749,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
+          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>Rc14af04e09</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics10060627</t>
+          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4796,34 +4796,34 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
+          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rc14af04e09</t>
+          <t>Rad03dbff94</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
+          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4868,19 +4868,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rad03dbff94</t>
+          <t>R4c045cf31e</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
+          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
+          <t>PMC5842392</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4930,14 +4930,14 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R4c045cf31e</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4957,17 +4957,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PMC5842392</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Artículo principal + Supplementary Table 1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 1</t>
+          <t>Artículo principal + Supplementary Table 2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 2</t>
+          <t>Artículo principal + Supplementary Table 3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 3</t>
+          <t>Artículo principal + Supplementary Table 4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5165,17 +5165,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rf9e8793e57</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5185,44 +5185,44 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 4</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rf9e8793e57</t>
+          <t>R0bfe86965a</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
+          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5267,19 +5267,19 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R0bfe86965a</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
+          <t>pmid:30884879; doi:10.3390/v11030265</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5309,34 +5309,34 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC6466067</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Ra48f1861e9</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>pmid:30884879; doi:10.3390/v11030265</t>
+          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>PMC6466067</t>
+          <t>PMC7854414</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
+          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5386,14 +5386,14 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
+          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ra48f1861e9</t>
+          <t>R82609ed7d3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
+          <t>doi:10.3390/antibiotics11101358</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PMC7854414</t>
+          <t>PMC9598433</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
+          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>R82609ed7d3</t>
+          <t>Ra969af6438</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics11101358</t>
+          <t>pmid:37243293; doi:10.3390/v15051210</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PMC9598433</t>
+          <t>PMC10223274</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
+          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ra969af6438</t>
+          <t>Re6bdbee7be</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>pmid:37243293; doi:10.3390/v15051210</t>
+          <t>doi:10.3390/antibiotics14020114</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PMC10223274</t>
+          <t>PMC11851713</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
+          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5557,14 +5557,14 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Re6bdbee7be</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14020114</t>
+          <t>doi:10.5005/jp-journals-10071-25143</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PMC11851713</t>
+          <t>PMC13177854</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5604,24 +5604,24 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
+          <t>L ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Manageme</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>bstract", "Patients and Methods", la Figura 1 de flujo de pacientes, la sección "Results</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Thera</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5631,54 +5631,54 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>Raa2e529a17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>doi:10.5005/jp-journals-10071-25143</t>
+          <t>doi:10.1002/central/cn-01142800/full</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>PMC13177854</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>L ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Manageme</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>bstract", "Patients and Methods", la Figura 1 de flujo de pacientes, la sección "Results</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Thera</t>
+          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5688,54 +5688,54 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raa2e529a17</t>
+          <t>Reba6a0e48c</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-01142800/full</t>
+          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC6090023</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reba6a0e48c</t>
+          <t>Rf76e86bc31</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5755,17 +5755,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
+          <t>doi:10.3389/fmed.2020.00342</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PMC6090023</t>
+          <t>PMC7410981</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
+          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rf76e86bc31</t>
+          <t>R36411565f8</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2020.00342</t>
+          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5822,34 +5822,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PMC7410981</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
+          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>R36411565f8</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
+          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5879,34 +5879,34 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC10573729</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
+          <t>doi:10.3390/antibiotics14010087</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PMC10573729</t>
+          <t>PMC11759190</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
+          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R157654d30f</t>
+          <t>R18831247ea</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14010087</t>
+          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5993,34 +5993,34 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PMC11759190</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
+          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>R18831247ea</t>
+          <t>R3ec3a782bb</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
+          <t>pmid:31548497; doi:10.3390/v11100891</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6065,19 +6065,19 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R3ec3a782bb</t>
+          <t>R9b7fc7c6a6</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>pmid:31548497; doi:10.3390/v11100891</t>
+          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6122,19 +6122,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>INTRODUCCION</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
+          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>R9b7fc7c6a6</t>
+          <t>Re6084b7743</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
+          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6179,19 +6179,19 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>INTRODUCCION</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
+          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Re6084b7743</t>
+          <t>Rd7ea09ed5c</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
+          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6221,34 +6221,34 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11341935</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rd7ea09ed5c</t>
+          <t>Rc513775cd3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
+          <t>doi:10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>PMC11341935</t>
+          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
+          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6298,14 +6298,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EST-170</t>
+          <t>EST-173</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rc513775cd3</t>
+          <t>R4a198d51c5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6323,11 +6323,7 @@
           <t>articulo</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.avsurg.2024.100302</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>1</t>
@@ -6335,34 +6331,34 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
+          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EST-173</t>
+          <t>EST-181</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6372,7 +6368,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>R4a198d51c5</t>
+          <t>Rf2699aa65a</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6380,7 +6376,11 @@
           <t>articulo</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>pmid:36851713; doi:10.1002/central/cn-02529947/full</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>1</t>
@@ -6388,34 +6388,34 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC9964274</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>s Article Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patient</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>metodos y analisis</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
+          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EST-181</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rf2699aa65a</t>
+          <t>R419c6f6d67</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>pmid:36851713; doi:10.1002/central/cn-02529947/full</t>
+          <t>doi:10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PMC9964274</t>
+          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6455,24 +6455,24 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>s Article Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patient</t>
+          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>metodos y analisis</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
+          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EST-184</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6482,17 +6482,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>R419c6f6d67</t>
+          <t>R95ed8fa775</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.jdcr.2026.06.010</t>
+          <t>doi:10.1002/central/cn-02203985/full</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6502,34 +6502,34 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
+          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EST-188</t>
+          <t>EST-208</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6539,17 +6539,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>R95ed8fa775</t>
+          <t>R48f287c11f</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-02203985/full</t>
+          <t>pmid:31651936; doi:10.1093/ejcts/ezz295</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6559,89 +6559,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>texto_cache/EST-208.txt</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>otapovEV.Treatmentofchronicleftventricularassistdeviceinfectionwithlocalappli</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>EST-208</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>R48f287c11f</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>pmid:31651936; doi:10.1093/ejcts/ezz295</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>texto_cache/EST-208.txt</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>otapovEV.Treatmentofchronicleftventricularassistdeviceinfectionwithlocalappli</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
           <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K104"/>
+  <autoFilter ref="A1:K103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>102 filas de datos</t>
+          <t>98 filas de datos</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1517,7 +1517,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-009</t>
+          <t>EST-010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R7f5e8ad26a</t>
+          <t>R65dafc8475</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>pmid:34177601; doi:10.3389/fphar.2021.692614</t>
+          <t>pmid:35869081; doi:10.1038/s41467-022-31837-9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC8222915</t>
+          <t>PMC9306240</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1557,24 +1557,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.692614 Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Mul</t>
+          <t>22-31837-9 Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudom</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Tabla 1 y tabla 2</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Multiple Failed Antibiotic Treatments.</t>
+          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-010</t>
+          <t>EST-011</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>R65dafc8475</t>
+          <t>R92e57101da</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>pmid:35869081; doi:10.1038/s41467-022-31837-9</t>
+          <t>pmid:41022989; doi:10.1038/s41598-025-17510-3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC9306240</t>
+          <t>PMC12480670</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22-31837-9 Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudom</t>
+          <t>orts OPEN A case report of bacteriophage therapy for the treatment of lung infection due to</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1624,14 +1624,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
+          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-011</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R92e57101da</t>
+          <t>R4097bfc5b7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>pmid:41022989; doi:10.1038/s41598-025-17510-3</t>
+          <t>pmid:42364990; doi:10.1038/s41467-026-74326-z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC12480670</t>
+          <t>https://www.nature.com/articles/s41467-026-74326-z_reference.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>orts OPEN A case report of bacteriophage therapy for the treatment of lung infection due to</t>
+          <t>e in Press Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosth</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
+          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-013</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R4097bfc5b7</t>
+          <t>R1283b43e8a</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>pmid:42364990; doi:10.1038/s41467-026-74326-z</t>
+          <t>doi:10.1016/j.hlife.2025.03.004</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41467-026-74326-z_reference.pdf</t>
+          <t>https://doi.org/10.1016/j.hlife.2025.03.004</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1728,24 +1728,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>e in Press Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosth</t>
+          <t>SE REPORT Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment</t>
+          <t>Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aeruginosa infections</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-013</t>
+          <t>EST-014</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R1283b43e8a</t>
+          <t>R5f5c60be8e</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.hlife.2025.03.004</t>
+          <t>pmid:35444073; doi:10.5582/bst.2022.01147</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.hlife.2025.03.004</t>
+          <t>https://www.jstage.jst.go.jp/article/bst/16/2/16_2022.01147/_pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1785,24 +1785,24 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SE REPORT Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aer</t>
+          <t>022.01147 Bacteriophage therapy for empyema caused by carbapenem- resistant Pseudomonas</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aeruginosa infections</t>
+          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-014</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R5f5c60be8e</t>
+          <t>Rc16977760e</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pmid:35444073; doi:10.5582/bst.2022.01147</t>
+          <t>pmid:35529052; doi:10.1093/jacamr/dlac046</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1832,34 +1832,34 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.jstage.jst.go.jp/article/bst/16/2/16_2022.01147/_pdf</t>
+          <t>https://academic.oup.com/jacamr/article-pdf/4/3/dlac046/45065070/dlac046.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>022.01147 Bacteriophage therapy for empyema caused by carbapenem- resistant Pseudomonas</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
+          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rc16977760e</t>
+          <t>R0145584831</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>pmid:35529052; doi:10.1093/jacamr/dlac046</t>
+          <t>pmid:35547216; doi:10.3389/fmed.2022.851310</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1889,17 +1889,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jacamr/article-pdf/4/3/dlac046/45065070/dlac046.pdf</t>
+          <t>PMC9081798</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>22.851310 Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Tr</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
+          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femu</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-018</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R0145584831</t>
+          <t>Raf45c3cf1c</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>pmid:35547216; doi:10.3389/fmed.2022.851310</t>
+          <t>pmid:40810649; doi:10.1080/1120009x.2025.2547147</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1946,34 +1946,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC9081798</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22.851310 Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Tr</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>na</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femu</t>
+          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-018</t>
+          <t>EST-019</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raf45c3cf1c</t>
+          <t>Rff26853b4a</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>pmid:40810649; doi:10.1080/1120009x.2025.2547147</t>
+          <t>pmid:38917792; doi:10.1016/j.medj.2024.05.017</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2003,34 +2003,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://doi.org/10.1016/j.medj.2024.05.017</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>se Report Neutralizing antibodies after nebulized phage therapy in cystic fibrosis pati</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
+          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-019</t>
+          <t>EST-021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rff26853b4a</t>
+          <t>R49b7551b94</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pmid:38917792; doi:10.1016/j.medj.2024.05.017</t>
+          <t>pmid:30292481; doi:10.1002/central/cn-01789457/full; nct:NCT02116010</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.medj.2024.05.017</t>
+          <t>texto_cache/EST-021.txt</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2070,24 +2070,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>se Report Neutralizing antibodies after nebulized phage therapy in cystic fibrosis pati</t>
+          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds i</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>FIGURA 1-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
+          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised,</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-021</t>
+          <t>EST-024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>R49b7551b94</t>
+          <t>Rc5f05c2543</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2107,44 +2107,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>pmid:30292481; doi:10.1002/central/cn-01789457/full; nct:NCT02116010</t>
+          <t>pmid:37515541; doi:10.1177/23247096231188243</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>texto_cache/EST-021.txt</t>
+          <t>PMC10387758</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds i</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>FIGURA 1-4</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised,</t>
+          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-024</t>
+          <t>EST-027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rc5f05c2543</t>
+          <t>R87db0a0109</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>pmid:37515541; doi:10.1177/23247096231188243</t>
+          <t>pmid:37369702; doi:10.1038/s41467-023-39370-z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2174,34 +2174,34 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC10387758</t>
+          <t>PMC10300124</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>23-39370-z Personalized aerosolised bacteriophage treatment of a chronic lung infection</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
+          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-027</t>
+          <t>EST-028</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>R87db0a0109</t>
+          <t>Re06c450e37</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>pmid:37369702; doi:10.1038/s41467-023-39370-z</t>
+          <t>pmid:40639454; doi:10.1016/j.jiac.2025.102770</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2231,34 +2231,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC10300124</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23-39370-z Personalized aerosolised bacteriophage treatment of a chronic lung infection</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
+          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EST-028</t>
+          <t>EST-029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Re06c450e37</t>
+          <t>R179a877749</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>pmid:40639454; doi:10.1016/j.jiac.2025.102770</t>
+          <t>pmid:39740667; doi:10.1002/central/cn-02799532/full; nct:NCT04803708</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2293,29 +2293,29 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>único artículo del grupo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>de los 4 informes del estudio, 3 son fichas de registro o resúmenes de congreso y uno solo es artículo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
+          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot u</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EST-029</t>
+          <t>EST-030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>R179a877749</t>
+          <t>R71c51137b3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2335,44 +2335,44 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>pmid:39740667; doi:10.1002/central/cn-02799532/full; nct:NCT04803708</t>
+          <t>pmid:41853116; doi:10.1128/asmcr.00108-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC12955376</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>único artículo del grupo</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>de los 4 informes del estudio, 3 son fichas de registro o resúmenes de congreso y uno solo es artículo</t>
+          <t>se Report Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infecti</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot u</t>
+          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EST-030</t>
+          <t>EST-031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R71c51137b3</t>
+          <t>Rad7d40f6e0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>pmid:41853116; doi:10.1128/asmcr.00108-25</t>
+          <t>doi:10.1016/j.medmic.2026.100178</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC12955376</t>
+          <t>https://doi.org/10.1016/j.medmic.2026.100178</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2412,24 +2412,24 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>se Report Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infecti</t>
+          <t>oecology Harnessing bacteriophages to combat antibiotic-resistant chronic postoperat</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
+          <t>Harnessing bacteriophages to combat antibiotic-resistant chronic postoperative infections: A promising case series</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EST-031</t>
+          <t>EST-032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rad7d40f6e0</t>
+          <t>R6556b80259</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.medmic.2026.100178</t>
+          <t>pmid:28992111; doi:10.1093/jpids/pix056</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2459,34 +2459,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.medmic.2026.100178</t>
+          <t>https://academic.oup.com/jpids/article-pdf/7/3/253/25505942/pix056.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>oecology Harnessing bacteriophages to combat antibiotic-resistant chronic postoperat</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Harnessing bacteriophages to combat antibiotic-resistant chronic postoperative infections: A promising case series</t>
+          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EST-032</t>
+          <t>EST-033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R6556b80259</t>
+          <t>R30e4263f97</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>pmid:28992111; doi:10.1093/jpids/pix056</t>
+          <t>pmid:31437402; doi:10.1164/rccm.201904-0839le</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jpids/article-pdf/7/3/253/25505942/pix056.pdf</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2536,14 +2536,14 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
+          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EST-033</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R30e4263f97</t>
+          <t>R239f702d9a</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>pmid:31437402; doi:10.1164/rccm.201904-0839le</t>
+          <t>pmid:33005701; doi:10.1093/ofid/ofaa389</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2573,34 +2573,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/ofid/article-pdf/7/9/ofaa389/33872731/ofaa389.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriopha</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
+          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R239f702d9a</t>
+          <t>R02b1e109ec</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>pmid:33005701; doi:10.1093/ofid/ofaa389</t>
+          <t>pmid:34696331; doi:10.3390/v13101901</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/article-pdf/7/9/ofaa389/33872731/ofaa389.pdf</t>
+          <t>https://www.mdpi.com/1999-4915/13/10/1901/pdf?version=1632361337</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>R ARTICLE Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriopha</t>
+          <t>seReport Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacte</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections a</t>
+          <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-039</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R02b1e109ec</t>
+          <t>R146b3e2f13</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>pmid:34696331; doi:10.3390/v13101901</t>
+          <t>doi:10.3390/antibiotics12121734</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/1999-4915/13/10/1901/pdf?version=1632361337</t>
+          <t>PMC10741035</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacte</t>
+          <t>s Article Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: No</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
+          <t>Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: Novel Protocol Description and Case Series</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EST-039</t>
+          <t>EST-040</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R146b3e2f13</t>
+          <t>R5b72edadd2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics12121734</t>
+          <t>pmid:37409241; doi:10.2147/idr.s413900</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC10741035</t>
+          <t>PMC10319284</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2754,24 +2754,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>s Article Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: No</t>
+          <t>SE REPORT Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Tra</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: Novel Protocol Description and Case Series</t>
+          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EST-040</t>
+          <t>EST-042</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R5b72edadd2</t>
+          <t>R35b74982e8</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>pmid:37409241; doi:10.2147/idr.s413900</t>
+          <t>pmid:41479406; doi:10.1002/mlf2.70042</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC10319284</t>
+          <t>PMC12754627</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2811,24 +2811,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SE REPORT Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Tra</t>
+          <t>SE REPORT Phage therapy of perinephric abscess in kidney ‐ transplantation recipients cau</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal</t>
+          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EST-042</t>
+          <t>EST-043</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R35b74982e8</t>
+          <t>R2105e151c4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>pmid:41479406; doi:10.1002/mlf2.70042</t>
+          <t>pmid:42263718; doi:10.1016/s1473-3099(26)00176-3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC12754627</t>
+          <t>texto_cache/EST-043.txt</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SE REPORT Phage therapy of perinephric abscess in kidney ‐ transplantation recipients cau</t>
+          <t>August 11. Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first exp</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
+          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in th</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EST-043</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R2105e151c4</t>
+          <t>Rdcfed12d81</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>pmid:42263718; doi:10.1016/s1473-3099(26)00176-3</t>
+          <t>pmid:41565011; doi:10.1016/j.jpeds.2026.115005</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>texto_cache/EST-043.txt</t>
+          <t>https://www.jpeds.com/article/S0022-3476(26)00033-8/pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>August 11. Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first exp</t>
+          <t>F REPORTS Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infecti</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in th</t>
+          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Y</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-045</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rdcfed12d81</t>
+          <t>R786d185312</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>pmid:41565011; doi:10.1016/j.jpeds.2026.115005</t>
+          <t>doi:10.20953/1729-9225-2017-4-49-54</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2972,34 +2972,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.jpeds.com/article/S0022-3476(26)00033-8/pdf</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>F REPORTS Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infecti</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Y</t>
+          <t>Concept of individualized medicine based on personalized phage therapy for intensive care unit patients suffering from healthcare-associated</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-045</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>R786d185312</t>
+          <t>Rb2ced3ce85</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>doi:10.20953/1729-9225-2017-4-49-54</t>
+          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3029,34 +3029,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC5460490</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Concept of individualized medicine based on personalized phage therapy for intensive care unit patients suffering from healthcare-associated</t>
+          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rb2ced3ce85</t>
+          <t>Red52d0884d</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
+          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC5460490</t>
+          <t>PMC7187616</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
+          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
+          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Red52d0884d</t>
+          <t>Rcdf0cd1678</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
+          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC7187616</t>
+          <t>PMC9969736</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
+          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
+          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rcdf0cd1678</t>
+          <t>R0785077af4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
+          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC9969736</t>
+          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
+          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R0785077af4</t>
+          <t>R50e1887412</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3247,44 +3247,44 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
+          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
+          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
+          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R50e1887412</t>
+          <t>R79b5603bcb</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3304,44 +3304,44 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
+          <t>doi:10.3389/fmed.2024.1428432</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
+          <t>PMC11272550</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
+          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>R79b5603bcb</t>
+          <t>R067acd0a39</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2024.1428432</t>
+          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC11272550</t>
+          <t>PMC11504013</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3391,14 +3391,14 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-054</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>R067acd0a39</t>
+          <t>Rb03837dd03</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
+          <t>pmid:39965256; doi:10.1097/mao.0000000000004417</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3428,34 +3428,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC11504013</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rb03837dd03</t>
+          <t>Rd428980732</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pmid:39965256; doi:10.1097/mao.0000000000004417</t>
+          <t>pmid:39861912; doi:10.3390/v17010123</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3485,34 +3485,34 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11768548</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R1705a32c41</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>doi:10.1097/cu9.0000000000000268</t>
+          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC12042198</t>
+          <t>PMC12530250</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3552,24 +3552,24 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>lArticle Bacteriophage therapy in women with chronic recurrent cystitis caused by multi</t>
+          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused by multidrug-resistant bacteria: A prospective, observational, compara</t>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rd428980732</t>
+          <t>R1add858cdd</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>pmid:39861912; doi:10.3390/v17010123</t>
+          <t>doi:10.20953/1729-9225-2017-1-35-40</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3599,34 +3599,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC11768548</t>
+          <t>https://zenodo.org/record/1997795</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+          <t>Anti-phage antibody response in phage therapy against healthcare-associated infections (HAIs)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R1705a32c41</t>
+          <t>R85f6503e9a</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
+          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC12530250</t>
+          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3666,24 +3666,24 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
+          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-059</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R1add858cdd</t>
+          <t>Rb506e81130</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>doi:10.20953/1729-9225-2017-1-35-40</t>
+          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3713,34 +3713,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://zenodo.org/record/1997795</t>
+          <t>PMC9523064</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Anti-phage antibody response in phage therapy against healthcare-associated infections (HAIs)</t>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R85f6503e9a</t>
+          <t>Rb93cd3cbd9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
+          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3770,34 +3770,34 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rb506e81130</t>
+          <t>Rdfeb34f4ef</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
+          <t>doi:10.1016/j.eimc.2025.05.008</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3827,34 +3827,34 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PMC9523064</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
+          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rb93cd3cbd9</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
+          <t>doi:10.1093/ofid/ofad221</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3884,34 +3884,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rdfeb34f4ef</t>
+          <t>R607037aeaa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.eimc.2025.05.008</t>
+          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3956,19 +3956,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
+          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>R93e07521e9</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>doi:10.1093/ofid/ofad221</t>
+          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
+          <t>PMC7277081</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
+          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
+          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R607037aeaa</t>
+          <t>R4e80e5028d</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
+          <t>doi:10.15789/1563-0625-pti-2012</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4055,34 +4055,34 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>R93e07521e9</t>
+          <t>Rf41ce1f437</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
+          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC7277081</t>
+          <t>PMC10989018</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4122,24 +4122,24 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
+          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>resumen materiales y metodos</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R4e80e5028d</t>
+          <t>Re9fa49ae6d</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>doi:10.15789/1563-0625-pti-2012</t>
+          <t>doi:10.1002/central/cn-02936419/full</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4169,34 +4169,34 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
+          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rf41ce1f437</t>
+          <t>Rde30f4212d</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
+          <t>doi:10.1089/phage.2020.0010</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC10989018</t>
+          <t>PMC9041461</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
+          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>resumen materiales y metodos</t>
+          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Re9fa49ae6d</t>
+          <t>Rbcb0bd26fd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-02936419/full</t>
+          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
+          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rde30f4212d</t>
+          <t>R188612f054</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>doi:10.1089/phage.2020.0010</t>
+          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC9041461</t>
+          <t>PMC10034620</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4350,24 +4350,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
+          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rbcb0bd26fd</t>
+          <t>R0b195c9d15</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
+          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11442429</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,19 +4412,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R188612f054</t>
+          <t>R72f673966a</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
+          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PMC10034620</t>
+          <t>PMC12786087</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4464,24 +4464,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
+          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R0b195c9d15</t>
+          <t>Rfc0fff7284</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
+          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PMC11442429</t>
+          <t>PMC12877064</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4531,14 +4531,14 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R72f673966a</t>
+          <t>Ra1f20b8500</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
+          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PMC12786087</t>
+          <t>PMC8422068</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4578,24 +4578,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
+          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rfc0fff7284</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
+          <t>doi:10.3390/antibiotics10060627</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PMC12877064</t>
+          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4635,24 +4635,24 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
+          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ra1f20b8500</t>
+          <t>Rc14af04e09</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
+          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4682,34 +4682,34 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PMC8422068</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>Rad03dbff94</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics10060627</t>
+          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4739,34 +4739,34 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
+          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rc14af04e09</t>
+          <t>R4c045cf31e</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
+          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4796,34 +4796,34 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC5842392</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rad03dbff94</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4843,54 +4843,54 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Artículo principal + Supplementary Table 1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R4c045cf31e</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PMC5842392</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Artículo principal + Supplementary Table 2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 1</t>
+          <t>Artículo principal + Supplementary Table 3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 2</t>
+          <t>Artículo principal + Supplementary Table 4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5051,17 +5051,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rf9e8793e57</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5071,54 +5071,54 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 3</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>R0bfe86965a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5128,44 +5128,44 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 4</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rf9e8793e57</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
+          <t>pmid:30884879; doi:10.3390/v11030265</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5195,34 +5195,34 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC6466067</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>R0bfe86965a</t>
+          <t>Ra48f1861e9</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
+          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5252,34 +5252,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC7854414</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
+          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R82609ed7d3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>pmid:30884879; doi:10.3390/v11030265</t>
+          <t>doi:10.3390/antibiotics11101358</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>PMC6466067</t>
+          <t>PMC9598433</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
+          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ra48f1861e9</t>
+          <t>Ra969af6438</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
+          <t>pmid:37243293; doi:10.3390/v15051210</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>PMC7854414</t>
+          <t>PMC10223274</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
+          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5386,14 +5386,14 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>R82609ed7d3</t>
+          <t>Re6bdbee7be</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics11101358</t>
+          <t>doi:10.3390/antibiotics14020114</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PMC9598433</t>
+          <t>PMC11851713</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
+          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ra969af6438</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5470,17 +5470,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>pmid:37243293; doi:10.3390/v15051210</t>
+          <t>doi:10.5005/jp-journals-10071-25143</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PMC10223274</t>
+          <t>PMC13177854</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5490,24 +5490,24 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
+          <t>L ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Manageme</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>bstract", "Patients and Methods", la Figura 1 de flujo de pacientes, la sección "Results</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Thera</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Re6bdbee7be</t>
+          <t>Raa2e529a17</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14020114</t>
+          <t>doi:10.1002/central/cn-01142800/full</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5537,34 +5537,34 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PMC11851713</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
+          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>Reba6a0e48c</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>doi:10.5005/jp-journals-10071-25143</t>
+          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PMC13177854</t>
+          <t>PMC6090023</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5604,24 +5604,24 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>L ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Manageme</t>
+          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bstract", "Patients and Methods", la Figura 1 de flujo de pacientes, la sección "Results</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Thera</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raa2e529a17</t>
+          <t>Rf76e86bc31</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-01142800/full</t>
+          <t>doi:10.3389/fmed.2020.00342</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5651,34 +5651,34 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC7410981</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Reba6a0e48c</t>
+          <t>R36411565f8</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5698,44 +5698,44 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
+          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>PMC6090023</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rf76e86bc31</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2020.00342</t>
+          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PMC7410981</t>
+          <t>PMC10573729</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
+          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>R36411565f8</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
+          <t>doi:10.3390/antibiotics14010087</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5822,34 +5822,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11759190</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R18831247ea</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
+          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5879,34 +5879,34 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PMC10573729</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
+          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>R157654d30f</t>
+          <t>R3ec3a782bb</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14010087</t>
+          <t>pmid:31548497; doi:10.3390/v11100891</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5936,34 +5936,34 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PMC11759190</t>
+          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R18831247ea</t>
+          <t>R9b7fc7c6a6</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
+          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6008,19 +6008,19 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
+          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>R3ec3a782bb</t>
+          <t>Re6084b7743</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>pmid:31548497; doi:10.3390/v11100891</t>
+          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6065,19 +6065,19 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
+          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>R9b7fc7c6a6</t>
+          <t>Rd7ea09ed5c</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
+          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6107,34 +6107,34 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11341935</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>INTRODUCCION</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Re6084b7743</t>
+          <t>Rc513775cd3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
+          <t>doi:10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6164,34 +6164,34 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-173</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rd7ea09ed5c</t>
+          <t>R4a198d51c5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6209,11 +6209,7 @@
           <t>articulo</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>1</t>
@@ -6221,34 +6217,34 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PMC11341935</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EST-170</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6258,7 +6254,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rc513775cd3</t>
+          <t>R419c6f6d67</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6268,7 +6264,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.avsurg.2024.100302</t>
+          <t>doi:10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6278,7 +6274,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
+          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6288,7 +6284,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
+          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6298,14 +6294,14 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
+          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EST-173</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6315,15 +6311,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>R4a198d51c5</t>
+          <t>R95ed8fa775</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>resumen de congreso</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>doi:10.1002/central/cn-02203985/full</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>1</t>
@@ -6351,240 +6351,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>EST-181</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Rf2699aa65a</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>pmid:36851713; doi:10.1002/central/cn-02529947/full</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>PMC9964274</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>s Article Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patient</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>metodos y analisis</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>R419c6f6d67</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>R95ed8fa775</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>resumen de congreso</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>doi:10.1002/central/cn-02203985/full</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
           <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>EST-208</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>R48f287c11f</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>pmid:31651936; doi:10.1093/ejcts/ezz295</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>texto_cache/EST-208.txt</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>otapovEV.Treatmentofchronicleftventricularassistdeviceinfectionwithlocalappli</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K103"/>
+  <autoFilter ref="A1:K99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>98 filas de datos</t>
+          <t>94 filas de datos</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2942,7 +2942,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-045</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>R786d185312</t>
+          <t>Rb2ced3ce85</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>doi:10.20953/1729-9225-2017-4-49-54</t>
+          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2972,34 +2972,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC5460490</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Concept of individualized medicine based on personalized phage therapy for intensive care unit patients suffering from healthcare-associated</t>
+          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rb2ced3ce85</t>
+          <t>Red52d0884d</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
+          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC5460490</t>
+          <t>PMC7187616</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
+          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3049,14 +3049,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
+          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Red52d0884d</t>
+          <t>Rcdf0cd1678</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
+          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC7187616</t>
+          <t>PMC9969736</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
+          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
+          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rcdf0cd1678</t>
+          <t>R0785077af4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
+          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC9969736</t>
+          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
+          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>R0785077af4</t>
+          <t>R50e1887412</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3190,44 +3190,44 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
+          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
+          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
+          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R50e1887412</t>
+          <t>R79b5603bcb</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3247,44 +3247,44 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
+          <t>doi:10.3389/fmed.2024.1428432</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
+          <t>PMC11272550</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
+          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R79b5603bcb</t>
+          <t>R067acd0a39</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2024.1428432</t>
+          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC11272550</t>
+          <t>PMC11504013</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3334,14 +3334,14 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-054</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>R067acd0a39</t>
+          <t>Rb03837dd03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
+          <t>pmid:39965256; doi:10.1097/mao.0000000000004417</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC11504013</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rb03837dd03</t>
+          <t>Rd428980732</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pmid:39965256; doi:10.1097/mao.0000000000004417</t>
+          <t>pmid:39861912; doi:10.3390/v17010123</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3428,34 +3428,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11768548</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rd428980732</t>
+          <t>R1705a32c41</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pmid:39861912; doi:10.3390/v17010123</t>
+          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC11768548</t>
+          <t>PMC12530250</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
+          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3505,14 +3505,14 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R1705a32c41</t>
+          <t>R85f6503e9a</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
+          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC12530250</t>
+          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3552,24 +3552,24 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
+          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-059</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>R1add858cdd</t>
+          <t>Rb506e81130</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>doi:10.20953/1729-9225-2017-1-35-40</t>
+          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3599,34 +3599,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://zenodo.org/record/1997795</t>
+          <t>PMC9523064</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Anti-phage antibody response in phage therapy against healthcare-associated infections (HAIs)</t>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-064</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R85f6503e9a</t>
+          <t>Rb93cd3cbd9</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
+          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3656,34 +3656,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-065</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rb506e81130</t>
+          <t>Rdfeb34f4ef</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
+          <t>doi:10.1016/j.eimc.2025.05.008</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3713,34 +3713,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC9523064</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
+          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rb93cd3cbd9</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
+          <t>doi:10.1093/ofid/ofad221</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3770,34 +3770,34 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-073</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rdfeb34f4ef</t>
+          <t>R607037aeaa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.eimc.2025.05.008</t>
+          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3842,19 +3842,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
+          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>R93e07521e9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>doi:10.1093/ofid/ofad221</t>
+          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
+          <t>PMC7277081</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3894,24 +3894,24 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
+          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
+          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R607037aeaa</t>
+          <t>R4e80e5028d</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
+          <t>doi:10.15789/1563-0625-pti-2012</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>R93e07521e9</t>
+          <t>Rf41ce1f437</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
+          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC7277081</t>
+          <t>PMC10989018</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
+          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>resumen materiales y metodos</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-078</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R4e80e5028d</t>
+          <t>Re9fa49ae6d</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>doi:10.15789/1563-0625-pti-2012</t>
+          <t>doi:10.1002/central/cn-02936419/full</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4055,34 +4055,34 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
+          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rf41ce1f437</t>
+          <t>Rde30f4212d</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
+          <t>doi:10.1089/phage.2020.0010</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC10989018</t>
+          <t>PMC9041461</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4122,24 +4122,24 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
+          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>resumen materiales y metodos</t>
+          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-081</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Re9fa49ae6d</t>
+          <t>Rbcb0bd26fd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-02936419/full</t>
+          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4189,14 +4189,14 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
+          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rde30f4212d</t>
+          <t>R188612f054</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>doi:10.1089/phage.2020.0010</t>
+          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC9041461</t>
+          <t>PMC10034620</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4236,24 +4236,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
+          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rbcb0bd26fd</t>
+          <t>R0b195c9d15</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
+          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11442429</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4298,19 +4298,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R188612f054</t>
+          <t>R72f673966a</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
+          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC10034620</t>
+          <t>PMC12786087</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4350,24 +4350,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
+          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R0b195c9d15</t>
+          <t>Rfc0fff7284</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
+          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4397,17 +4397,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PMC11442429</t>
+          <t>PMC12877064</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R72f673966a</t>
+          <t>Ra1f20b8500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
+          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PMC12786087</t>
+          <t>PMC8422068</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4464,24 +4464,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
+          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rfc0fff7284</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
+          <t>doi:10.3390/antibiotics10060627</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PMC12877064</t>
+          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
+          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-098</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ra1f20b8500</t>
+          <t>Rc14af04e09</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
+          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4568,34 +4568,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PMC8422068</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>Rad03dbff94</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics10060627</t>
+          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4625,34 +4625,34 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
+          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rc14af04e09</t>
+          <t>R4c045cf31e</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
+          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4682,34 +4682,34 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC5842392</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rad03dbff94</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4729,54 +4729,54 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Artículo principal + Supplementary Table 1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R4c045cf31e</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PMC5842392</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Artículo principal + Supplementary Table 2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 1</t>
+          <t>Artículo principal + Supplementary Table 3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 2</t>
+          <t>Artículo principal + Supplementary Table 4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4937,17 +4937,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-110</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rf9e8793e57</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4957,54 +4957,54 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 3</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-115</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>R0bfe86965a</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5014,44 +5014,44 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 4</t>
+          <t>abstracto</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EST-110</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rf9e8793e57</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
+          <t>pmid:30884879; doi:10.3390/v11030265</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5081,34 +5081,34 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC6466067</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EST-115</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R0bfe86965a</t>
+          <t>Ra48f1861e9</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
+          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5138,34 +5138,34 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC7854414</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
+          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R82609ed7d3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>pmid:30884879; doi:10.3390/v11030265</t>
+          <t>doi:10.3390/antibiotics11101358</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>PMC6466067</t>
+          <t>PMC9598433</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
+          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5215,14 +5215,14 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EST-117</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ra48f1861e9</t>
+          <t>Ra969af6438</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
+          <t>pmid:37243293; doi:10.3390/v15051210</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>PMC7854414</t>
+          <t>PMC10223274</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
+          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EST-121</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R82609ed7d3</t>
+          <t>Re6bdbee7be</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics11101358</t>
+          <t>doi:10.3390/antibiotics14020114</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>PMC9598433</t>
+          <t>PMC11851713</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
+          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-133</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ra969af6438</t>
+          <t>Raa2e529a17</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>pmid:37243293; doi:10.3390/v15051210</t>
+          <t>doi:10.1002/central/cn-01142800/full</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5366,34 +5366,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>PMC10223274</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
+          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Re6bdbee7be</t>
+          <t>Reba6a0e48c</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14020114</t>
+          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PMC11851713</t>
+          <t>PMC6090023</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
+          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>Rf76e86bc31</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5470,17 +5470,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>doi:10.5005/jp-journals-10071-25143</t>
+          <t>doi:10.3389/fmed.2020.00342</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PMC13177854</t>
+          <t>PMC7410981</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5490,24 +5490,24 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>L ARTICLE Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Manageme</t>
+          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>bstract", "Patients and Methods", la Figura 1 de flujo de pacientes, la sección "Results</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Thera</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EST-133</t>
+          <t>EST-140</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raa2e529a17</t>
+          <t>R36411565f8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-01142800/full</t>
+          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5557,14 +5557,14 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
+          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Reba6a0e48c</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
+          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PMC6090023</t>
+          <t>PMC10573729</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
+          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5614,14 +5614,14 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rf76e86bc31</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2020.00342</t>
+          <t>doi:10.3390/antibiotics14010087</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>PMC7410981</t>
+          <t>PMC11759190</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
+          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5671,14 +5671,14 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EST-140</t>
+          <t>EST-157</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>R36411565f8</t>
+          <t>R18831247ea</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
+          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5728,14 +5728,14 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
+          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R3ec3a782bb</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
+          <t>pmid:31548497; doi:10.3390/v11100891</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5765,34 +5765,34 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PMC10573729</t>
+          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EST-152</t>
+          <t>EST-165</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>R157654d30f</t>
+          <t>R9b7fc7c6a6</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics14010087</t>
+          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5822,34 +5822,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PMC11759190</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
+          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EST-157</t>
+          <t>EST-167</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>R18831247ea</t>
+          <t>Re6084b7743</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
+          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5899,14 +5899,14 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
+          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>R3ec3a782bb</t>
+          <t>Rd7ea09ed5c</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>pmid:31548497; doi:10.3390/v11100891</t>
+          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5936,34 +5936,34 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
+          <t>PMC11341935</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EST-165</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>R9b7fc7c6a6</t>
+          <t>Rc513775cd3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
+          <t>doi:10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5993,34 +5993,34 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>INTRODUCCION</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EST-167</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Re6084b7743</t>
+          <t>R419c6f6d67</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
+          <t>doi:10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6050,34 +6050,34 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
+          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-188</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6087,17 +6087,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rd7ea09ed5c</t>
+          <t>R95ed8fa775</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>articulo</t>
+          <t>resumen de congreso</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
+          <t>doi:10.1002/central/cn-02203985/full</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6107,256 +6107,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PMC11341935</t>
+          <t>sin texto</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>EST-170</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Rc513775cd3</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.avsurg.2024.100302</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>EST-173</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>R4a198d51c5</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>R419c6f6d67</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>R95ed8fa775</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>resumen de congreso</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>doi:10.1002/central/cn-02203985/full</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
           <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K99"/>
+  <autoFilter ref="A1:K95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>94 filas de datos</t>
+          <t>73 filas de datos</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1289,7 +1289,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-005</t>
+          <t>EST-006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R1d5dcd7d44</t>
+          <t>Rd3f6adc58a</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pmid:31102236; doi:10.1007/s15010-019-01319-0</t>
+          <t>pmid:39066242; doi:10.3390/v16071080</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1319,34 +1319,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11281479</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>seReport Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseud</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>Tabla 1 figura 2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Successful adjunctive use of bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa infection in a cystic fibrosi</t>
+          <t>Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseudomonas aeruginosa Responsible for Relapsing Ventilator-Associ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-006</t>
+          <t>EST-007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rd3f6adc58a</t>
+          <t>Rc6db9630c3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>pmid:39066242; doi:10.3390/v16071080</t>
+          <t>pmid:42070625; doi:10.1016/j.ijid.2026.108756</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PMC11281479</t>
+          <t>https://www.ijidonline.com/article/S1201-9712(26)00391-7/pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1386,24 +1386,24 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseud</t>
+          <t>se Report Adjuvant multisite bacteriophage cocktail administration as salvage treatme</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tabla 1 figura 2</t>
+          <t>Presentación del caso</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseudomonas aeruginosa Responsible for Relapsing Ventilator-Associ</t>
+          <t>Adjuvant multisite bacteriophage cocktail administration as salvage treatment in a patient with a multidrug-resistant Pseudomonas aeruginosa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-007</t>
+          <t>EST-008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rc6db9630c3</t>
+          <t>R1907f2a97a</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>pmid:42070625; doi:10.1016/j.ijid.2026.108756</t>
+          <t>pmid:40593506; doi:10.1002/central/cn-02878028/full</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.ijidonline.com/article/S1201-9712(26)00391-7/pdf</t>
+          <t>PMC12216271</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1443,24 +1443,24 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>se Report Adjuvant multisite bacteriophage cocktail administration as salvage treatme</t>
+          <t>25-60598-4 Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas fi aerugi</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Presentación del caso</t>
+          <t>EN METODOS Y EN CLINICAL TRIAL</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Adjuvant multisite bacteriophage cocktail administration as salvage treatment in a patient with a multidrug-resistant Pseudomonas aeruginosa</t>
+          <t xml:space="preserve">Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas aeruginosa infections in cystic fibrosis: a randomized first-in-human </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-008</t>
+          <t>EST-010</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>R1907f2a97a</t>
+          <t>R65dafc8475</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>pmid:40593506; doi:10.1002/central/cn-02878028/full</t>
+          <t>pmid:35869081; doi:10.1038/s41467-022-31837-9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC12216271</t>
+          <t>PMC9306240</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1500,24 +1500,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25-60598-4 Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas fi aerugi</t>
+          <t>22-31837-9 Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudom</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>EN METODOS Y EN CLINICAL TRIAL</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas aeruginosa infections in cystic fibrosis: a randomized first-in-human </t>
+          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-010</t>
+          <t>EST-011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R65dafc8475</t>
+          <t>R92e57101da</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>pmid:35869081; doi:10.1038/s41467-022-31837-9</t>
+          <t>pmid:41022989; doi:10.1038/s41598-025-17510-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC9306240</t>
+          <t>PMC12480670</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22-31837-9 Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudom</t>
+          <t>orts OPEN A case report of bacteriophage therapy for the treatment of lung infection due to</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1567,14 +1567,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
+          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-011</t>
+          <t>EST-012</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>R92e57101da</t>
+          <t>R4097bfc5b7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>pmid:41022989; doi:10.1038/s41598-025-17510-3</t>
+          <t>pmid:42364990; doi:10.1038/s41467-026-74326-z</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC12480670</t>
+          <t>https://www.nature.com/articles/s41467-026-74326-z_reference.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1614,24 +1614,24 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>orts OPEN A case report of bacteriophage therapy for the treatment of lung infection due to</t>
+          <t>e in Press Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosth</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
+          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-012</t>
+          <t>EST-013</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R4097bfc5b7</t>
+          <t>R1283b43e8a</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>pmid:42364990; doi:10.1038/s41467-026-74326-z</t>
+          <t>doi:10.1016/j.hlife.2025.03.004</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41467-026-74326-z_reference.pdf</t>
+          <t>https://doi.org/10.1016/j.hlife.2025.03.004</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1671,24 +1671,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>e in Press Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosth</t>
+          <t>SE REPORT Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aer</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>Resultados</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment</t>
+          <t>Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aeruginosa infections</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-013</t>
+          <t>EST-014</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R1283b43e8a</t>
+          <t>R5f5c60be8e</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.hlife.2025.03.004</t>
+          <t>pmid:35444073; doi:10.5582/bst.2022.01147</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.hlife.2025.03.004</t>
+          <t>https://www.jstage.jst.go.jp/article/bst/16/2/16_2022.01147/_pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1728,24 +1728,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SE REPORT Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aer</t>
+          <t>022.01147 Bacteriophage therapy for empyema caused by carbapenem- resistant Pseudomonas</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Resultados</t>
+          <t>Resumen</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aeruginosa infections</t>
+          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-014</t>
+          <t>EST-015</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R5f5c60be8e</t>
+          <t>Rc16977760e</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>pmid:35444073; doi:10.5582/bst.2022.01147</t>
+          <t>pmid:35529052; doi:10.1093/jacamr/dlac046</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1775,34 +1775,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.jstage.jst.go.jp/article/bst/16/2/16_2022.01147/_pdf</t>
+          <t>https://academic.oup.com/jacamr/article-pdf/4/3/dlac046/45065070/dlac046.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>022.01147 Bacteriophage therapy for empyema caused by carbapenem- resistant Pseudomonas</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Resumen</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
+          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-015</t>
+          <t>EST-016</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rc16977760e</t>
+          <t>R0145584831</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>pmid:35529052; doi:10.1093/jacamr/dlac046</t>
+          <t>pmid:35547216; doi:10.3389/fmed.2022.851310</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jacamr/article-pdf/4/3/dlac046/45065070/dlac046.pdf</t>
+          <t>PMC9081798</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>22.851310 Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Tr</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1852,14 +1852,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
+          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femu</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-016</t>
+          <t>EST-019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R0145584831</t>
+          <t>Rff26853b4a</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>pmid:35547216; doi:10.3389/fmed.2022.851310</t>
+          <t>pmid:38917792; doi:10.1016/j.medj.2024.05.017</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC9081798</t>
+          <t>https://doi.org/10.1016/j.medj.2024.05.017</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22.851310 Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Tr</t>
+          <t>se Report Neutralizing antibodies after nebulized phage therapy in cystic fibrosis pati</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femu</t>
+          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-018</t>
+          <t>EST-021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raf45c3cf1c</t>
+          <t>R49b7551b94</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1936,44 +1936,44 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>pmid:40810649; doi:10.1080/1120009x.2025.2547147</t>
+          <t>pmid:30292481; doi:10.1002/central/cn-01789457/full; nct:NCT02116010</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>texto_cache/EST-021.txt</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds i</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>FIGURA 1-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
+          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-019</t>
+          <t>EST-024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rff26853b4a</t>
+          <t>Rc5f05c2543</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>pmid:38917792; doi:10.1016/j.medj.2024.05.017</t>
+          <t>pmid:37515541; doi:10.1177/23247096231188243</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2003,34 +2003,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.medj.2024.05.017</t>
+          <t>PMC10387758</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>se Report Neutralizing antibodies after nebulized phage therapy in cystic fibrosis pati</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
+          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-021</t>
+          <t>EST-027</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>R49b7551b94</t>
+          <t>R87db0a0109</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pmid:30292481; doi:10.1002/central/cn-01789457/full; nct:NCT02116010</t>
+          <t>pmid:37369702; doi:10.1038/s41467-023-39370-z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>texto_cache/EST-021.txt</t>
+          <t>PMC10300124</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2070,24 +2070,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds i</t>
+          <t>23-39370-z Personalized aerosolised bacteriophage treatment of a chronic lung infection</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>FIGURA 1-4</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised,</t>
+          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-024</t>
+          <t>EST-030</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rc5f05c2543</t>
+          <t>R71c51137b3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>pmid:37515541; doi:10.1177/23247096231188243</t>
+          <t>pmid:41853116; doi:10.1128/asmcr.00108-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2117,34 +2117,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC10387758</t>
+          <t>PMC12955376</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>se Report Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infecti</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
+          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-027</t>
+          <t>EST-031</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R87db0a0109</t>
+          <t>Rad7d40f6e0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>pmid:37369702; doi:10.1038/s41467-023-39370-z</t>
+          <t>doi:10.1016/j.medmic.2026.100178</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC10300124</t>
+          <t>https://doi.org/10.1016/j.medmic.2026.100178</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2184,24 +2184,24 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23-39370-z Personalized aerosolised bacteriophage treatment of a chronic lung infection</t>
+          <t>oecology Harnessing bacteriophages to combat antibiotic-resistant chronic postoperat</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
+          <t>Harnessing bacteriophages to combat antibiotic-resistant chronic postoperative infections: A promising case series</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-028</t>
+          <t>EST-034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Re06c450e37</t>
+          <t>R239f702d9a</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>pmid:40639454; doi:10.1016/j.jiac.2025.102770</t>
+          <t>pmid:33005701; doi:10.1093/ofid/ofaa389</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://academic.oup.com/ofid/article-pdf/7/9/ofaa389/33872731/ofaa389.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriopha</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
+          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EST-029</t>
+          <t>EST-038</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>R179a877749</t>
+          <t>R02b1e109ec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2278,44 +2278,44 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>pmid:39740667; doi:10.1002/central/cn-02799532/full; nct:NCT04803708</t>
+          <t>pmid:34696331; doi:10.3390/v13101901</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mdpi.com/1999-4915/13/10/1901/pdf?version=1632361337</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>único artículo del grupo</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>de los 4 informes del estudio, 3 son fichas de registro o resúmenes de congreso y uno solo es artículo</t>
+          <t>seReport Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacte</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot u</t>
+          <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EST-030</t>
+          <t>EST-039</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>R71c51137b3</t>
+          <t>R146b3e2f13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>pmid:41853116; doi:10.1128/asmcr.00108-25</t>
+          <t>doi:10.3390/antibiotics12121734</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC12955376</t>
+          <t>PMC10741035</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2355,24 +2355,24 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>se Report Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infecti</t>
+          <t>s Article Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: No</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
+          <t>Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: Novel Protocol Description and Case Series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EST-031</t>
+          <t>EST-040</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rad7d40f6e0</t>
+          <t>R5b72edadd2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.medmic.2026.100178</t>
+          <t>pmid:37409241; doi:10.2147/idr.s413900</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.medmic.2026.100178</t>
+          <t>PMC10319284</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2412,24 +2412,24 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>oecology Harnessing bacteriophages to combat antibiotic-resistant chronic postoperat</t>
+          <t>SE REPORT Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Tra</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Harnessing bacteriophages to combat antibiotic-resistant chronic postoperative infections: A promising case series</t>
+          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EST-032</t>
+          <t>EST-042</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R6556b80259</t>
+          <t>R35b74982e8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>pmid:28992111; doi:10.1093/jpids/pix056</t>
+          <t>pmid:41479406; doi:10.1002/mlf2.70042</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2459,34 +2459,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jpids/article-pdf/7/3/253/25505942/pix056.pdf</t>
+          <t>PMC12754627</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>SE REPORT Phage therapy of perinephric abscess in kidney ‐ transplantation recipients cau</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
+          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EST-033</t>
+          <t>EST-043</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R30e4263f97</t>
+          <t>R2105e151c4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>pmid:31437402; doi:10.1164/rccm.201904-0839le</t>
+          <t>pmid:42263718; doi:10.1016/s1473-3099(26)00176-3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>texto_cache/EST-043.txt</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>August 11. Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first exp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
+          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in th</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EST-034</t>
+          <t>EST-044</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R239f702d9a</t>
+          <t>Rdcfed12d81</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>pmid:33005701; doi:10.1093/ofid/ofaa389</t>
+          <t>pmid:41565011; doi:10.1016/j.jpeds.2026.115005</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/article-pdf/7/9/ofaa389/33872731/ofaa389.pdf</t>
+          <t>https://www.jpeds.com/article/S0022-3476(26)00033-8/pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2583,24 +2583,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>R ARTICLE Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriopha</t>
+          <t>F REPORTS Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infecti</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections a</t>
+          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Y</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EST-038</t>
+          <t>EST-046</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R02b1e109ec</t>
+          <t>Rb2ced3ce85</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>pmid:34696331; doi:10.3390/v13101901</t>
+          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/1999-4915/13/10/1901/pdf?version=1632361337</t>
+          <t>PMC5460490</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2640,24 +2640,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacte</t>
+          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
+          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EST-039</t>
+          <t>EST-047</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R146b3e2f13</t>
+          <t>Red52d0884d</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics12121734</t>
+          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC10741035</t>
+          <t>PMC7187616</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>s Article Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: No</t>
+          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: Novel Protocol Description and Case Series</t>
+          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EST-040</t>
+          <t>EST-048</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R5b72edadd2</t>
+          <t>Rcdf0cd1678</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>pmid:37409241; doi:10.2147/idr.s413900</t>
+          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC10319284</t>
+          <t>PMC9969736</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SE REPORT Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Tra</t>
+          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal</t>
+          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EST-042</t>
+          <t>EST-049</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R35b74982e8</t>
+          <t>R0785077af4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>pmid:41479406; doi:10.1002/mlf2.70042</t>
+          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2801,34 +2801,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC12754627</t>
+          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SE REPORT Phage therapy of perinephric abscess in kidney ‐ transplantation recipients cau</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
+          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EST-043</t>
+          <t>EST-050</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R2105e151c4</t>
+          <t>R50e1887412</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>pmid:42263718; doi:10.1016/s1473-3099(26)00176-3</t>
+          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>texto_cache/EST-043.txt</t>
+          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>August 11. Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first exp</t>
+          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in th</t>
+          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EST-044</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rdcfed12d81</t>
+          <t>R79b5603bcb</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>pmid:41565011; doi:10.1016/j.jpeds.2026.115005</t>
+          <t>doi:10.3389/fmed.2024.1428432</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2915,17 +2915,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.jpeds.com/article/S0022-3476(26)00033-8/pdf</t>
+          <t>PMC11272550</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>F REPORTS Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infecti</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Y</t>
+          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EST-046</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rb2ced3ce85</t>
+          <t>R067acd0a39</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>pmid:28583189; doi:10.1186/s13054-017-1709-y</t>
+          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PMC5460490</t>
+          <t>PMC11504013</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>en Access Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas a</t>
+          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2992,14 +2992,14 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a</t>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EST-047</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Red52d0884d</t>
+          <t>Rd428980732</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>pmid:31527029; doi:10.1128/aac.00924-19</t>
+          <t>pmid:39861912; doi:10.3390/v17010123</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC7187616</t>
+          <t>PMC11768548</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CE crossm Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic</t>
+          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3049,14 +3049,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeru</t>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EST-048</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rcdf0cd1678</t>
+          <t>R1705a32c41</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>pmid:36861092; doi:10.1093/ofid/ofad051</t>
+          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC9969736</t>
+          <t>PMC12530250</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>R ARTICLE Application of Phage Therapy in a Case of a Chronic Hip- Prosthetic Joint Infectio</t>
+          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Exper</t>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EST-049</t>
+          <t>EST-061</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>R0785077af4</t>
+          <t>R85f6503e9a</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>pmid:36082999; doi:10.1093/infdis/jiac368</t>
+          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3143,34 +3143,34 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jid/article-pdf/227/3/311/49090233/jiac368.pdf</t>
+          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pn</t>
+          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EST-050</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>R50e1887412</t>
+          <t>Rb506e81130</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pmid:39491599; doi:10.1016/j.ijantimicag.2024.107372; nct:NCT05883995</t>
+          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijantimicag.2024.107372</t>
+          <t>PMC9523064</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3210,24 +3210,24 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>nication Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the P</t>
+          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R79b5603bcb</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>doi:10.3389/fmed.2024.1428432</t>
+          <t>doi:10.1093/ofid/ofad221</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3257,34 +3257,34 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PMC11272550</t>
+          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application an</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-074</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R067acd0a39</t>
+          <t>R93e07521e9</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pmid:39452183; doi:10.3390/antibiotics13100916</t>
+          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC11504013</t>
+          <t>PMC7277081</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3324,24 +3324,24 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>seReport Phage–Antibiotic Combination Therapy against Recurrent Pseudomonas Septicae</t>
+          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>DISEÑO Y METODOS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EST-054</t>
+          <t>EST-075</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rb03837dd03</t>
+          <t>R4e80e5028d</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pmid:39965256; doi:10.1097/mao.0000000000004417</t>
+          <t>doi:10.15789/1563-0625-pti-2012</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-077</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rd428980732</t>
+          <t>Rf41ce1f437</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pmid:39861912; doi:10.3390/v17010123</t>
+          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC11768548</t>
+          <t>PMC10989018</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3438,24 +3438,24 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>seReport Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Benta</t>
+          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>resumen materiales y metodos</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-080</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>R1705a32c41</t>
+          <t>Rde30f4212d</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>pmid:41244966; doi:10.1128/asmcr.00058-24</t>
+          <t>doi:10.1089/phage.2020.0010</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC12530250</t>
+          <t>PMC9041461</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>se Report Resolution of acute rejection in a bilateral double-lung transplanted cystic fi</t>
+          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>MATERILAES Y METODOS</t>
+          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EST-061</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R85f6503e9a</t>
+          <t>R188612f054</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>pmid:31207123; doi:10.1111/ajt.15503</t>
+          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/pdfdirect/10.1111/ajt.15503</t>
+          <t>PMC10034620</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3552,24 +3552,24 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NICATION Early clinical experience of bacteriophage therapy in 3 lung transplant recipi</t>
+          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rb506e81130</t>
+          <t>R0b195c9d15</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>pmid:36175406; doi:10.1038/s41467-022-33294-w</t>
+          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3599,17 +3599,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC9523064</t>
+          <t>PMC11442429</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>22-33294-w Bacteriophage-antibiotic combination ther- apy against extensively drug-resis</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3619,14 +3619,14 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantat</t>
+          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EST-064</t>
+          <t>EST-091</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rb93cd3cbd9</t>
+          <t>R72f673966a</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>pmid:40975185; doi:10.1016/j.ijantimicag.2025.107629</t>
+          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3656,34 +3656,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC12786087</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EST-065</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rdfeb34f4ef</t>
+          <t>Rfc0fff7284</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>doi:10.1016/j.eimc.2025.05.008</t>
+          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3713,34 +3713,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC12877064</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección pe</t>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Ra1f20b8500</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>doi:10.1093/ofid/ofad221</t>
+          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/ofid/advance-article-pdf/doi/10.1093/ofid/ofad221/50046439/ofad22</t>
+          <t>PMC8422068</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3780,24 +3780,24 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>R ARTICLE Compassionate Use of Bacteriophages for Failed Persistent Infections During t</t>
+          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli Phage Therapy Center</t>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EST-073</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R607037aeaa</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>pmid:31081402; doi:10.1177/1534734619835115</t>
+          <t>doi:10.3390/antibiotics10060627</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3827,34 +3827,34 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EST-074</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R93e07521e9</t>
+          <t>Rad03dbff94</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>pmid:32380707; doi:10.3390/antibiotics9050232</t>
+          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3884,34 +3884,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC7277081</t>
+          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>seReport Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surg</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>DISEÑO Y METODOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EST-075</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R4e80e5028d</t>
+          <t>R4c045cf31e</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>doi:10.15789/1563-0625-pti-2012</t>
+          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.mimmun.ru/mimmun/article/download/2012/1358</t>
+          <t>PMC5842392</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ibiotic resistant «Фаготерапия антибиотикорезистентной пневмонии: pneumonia: immunomodulation or redistribution?”, Medical иммуномодуляц</t>
+          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?; [ФАГОТЕРАПИЯ АНТИБИОТИКОРЕЗИСТЕНТНОЙ ПНЕВМОНИИ: ИММУНО</t>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EST-077</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rf41ce1f437</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3988,17 +3988,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>pmid:38470133; doi:10.1128/aac.01728-23</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC10989018</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4008,91 +4008,91 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ngth Text Pseudomonas aeruginosa ventricular assist device infections: findings from in</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>resumen materiales y metodos</t>
+          <t>Artículo principal + Supplementary Table 1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST-078</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Re9fa49ae6d</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>resumen de congreso</t>
+          <t>articulo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>doi:10.1002/central/cn-02936419/full</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Artículo principal + Supplementary Table 2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST-080</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rde30f4212d</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>doi:10.1089/phage.2020.0010</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC9041461</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4122,34 +4122,34 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2020.0010 Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infe</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>INTRODUCCION CASE 4 Y RESULTADOS</t>
+          <t>Artículo principal + Supplementary Table 3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EST-081</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rbcb0bd26fd</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4159,44 +4159,44 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>pmid:32657966; doi:10.1097/qco.0000000000000658</t>
+          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC11153159</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Artículo principal + Supplementary Table 4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>R188612f054</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>pmid:36636832; doi:10.1111/1751-7915.14217</t>
+          <t>pmid:30884879; doi:10.3390/v11030265</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC10034620</t>
+          <t>PMC6466067</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EF REPORT First- in- human application of double- stranded RNA bacteriophage in the treatmen</t>
+          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4246,14 +4246,14 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-117</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>R0b195c9d15</t>
+          <t>Ra48f1861e9</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>pmid:39355265; doi:10.3389/fcimb.2024.1354681</t>
+          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PMC11442429</t>
+          <t>PMC7854414</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-</t>
+          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EST-091</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R72f673966a</t>
+          <t>R82609ed7d3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>pmid:41516055; doi:10.3390/ijms27010172</t>
+          <t>doi:10.3390/antibiotics11101358</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC12786087</t>
+          <t>PMC9598433</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4350,24 +4350,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Article Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiv</t>
+          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Abstract, Sección 2.1 (Tabla 1) y Sección 4.1 (Materiales y Métodos)</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rfc0fff7284</t>
+          <t>Ra969af6438</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>pmid:41513696; doi:10.1038/s41467-025-68136-y</t>
+          <t>pmid:37243293; doi:10.3390/v15051210</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PMC12877064</t>
+          <t>PMC10223274</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>25-68136-y Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas a</t>
+          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4417,14 +4417,14 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ra1f20b8500</t>
+          <t>Re6bdbee7be</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>pmid:34369652; doi:10.15252/emmm.202113936</t>
+          <t>doi:10.3390/antibiotics14020114</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PMC8422068</t>
+          <t>PMC11851713</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Report Bacterial lysis, autophagy and innate immune responses during adjunctive phage</t>
+          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4474,14 +4474,14 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>Reba6a0e48c</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>doi:10.3390/antibiotics10060627</t>
+          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2079-6382/10/6/627/pdf?version=1621924381</t>
+          <t>PMC6090023</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>nication Low Immunogenicity of Intravesical Phage Therapy for Urogenitary Tract Infect</t>
+          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EST-098</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rc14af04e09</t>
+          <t>Rf76e86bc31</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>pmid:35183435; doi:10.1016/j.healun.2022.01.018</t>
+          <t>doi:10.3389/fmed.2020.00342</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4568,34 +4568,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>sin texto</t>
+          <t>PMC7410981</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>abstracto</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rad03dbff94</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>pmid:30060002; doi:10.1093/jac/dky263</t>
+          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4625,17 +4625,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/jac/article-pdf/73/10/2901/25770367/dky263.pdf</t>
+          <t>PMC10573729</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>informe único</t>
+          <t>título localizado en el texto leído</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
+          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selec</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R4c045cf31e</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>pmid:29588855; doi:10.1093/emph/eoy005</t>
+          <t>doi:10.3390/antibiotics14010087</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PMC5842392</t>
+          <t>PMC11759190</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ph/eoy005 Phage treatment of an aortic graft infected with Pseudomonas aeruginosa Benjam</t>
+          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>R3ec3a782bb</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4729,54 +4729,54 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:31548497; doi:10.3390/v11100891</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>título localizado en el texto leído</t>
+          <t>informe único</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 1</t>
+          <t>INTRODUCCION Y RESULTADOS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-169</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rd7ea09ed5c</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>PMC11341935</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4806,34 +4806,34 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 2</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rc513775cd3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>doi:10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4863,34 +4863,34 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 3</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>R419c6f6d67</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>pmid:38834776; doi:10.1038/s41564-024-01705-x; nct:NCT05498363</t>
+          <t>doi:10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PMC11153159</t>
+          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4920,1219 +4920,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>24-01705-x Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multi</t>
+          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Artículo principal + Supplementary Table 4</t>
+          <t>MATERILAES Y METODOS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospective observational study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>EST-110</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Rf9e8793e57</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>pmid:38066373; doi:10.1007/978-1-0716-3523-0_15</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>EST-115</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>R0bfe86965a</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>pmid:27643529; doi:10.2217/fmb-2016-0156</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>abstracto</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>EST-116</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Rb9ec93cff9</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>pmid:30884879; doi:10.3390/v11030265</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>PMC6466067</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>nication Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Iden</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>EST-117</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ra48f1861e9</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>pmid:33126265; doi:10.1007/s12223-020-00835-z</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>PMC7854414</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>NICATION Anti-phage serum antibody responses and the outcome of phage therapy M.Łusiak-Sz</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>EST-121</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>R82609ed7d3</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>doi:10.3390/antibiotics11101358</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>PMC9598433</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>nication Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report Marza</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>EST-124</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ra969af6438</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>pmid:37243293; doi:10.3390/v15051210</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>PMC10223274</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>s Article Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-R</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Dr</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EST-129</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Re6bdbee7be</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>doi:10.3390/antibiotics14020114</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>PMC11851713</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Article Phage Therapy for Orthopaedic Infections: The First Three Cases from the United K</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>EST-133</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Raa2e529a17</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>resumen de congreso</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>doi:10.1002/central/cn-01142800/full</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially avail</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>EST-134</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Reba6a0e48c</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>pmid:30131795; doi:10.1002/central/cn-01629006/full</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>PMC6090023</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>018.01832 Adapted Bacteriophages for Treating Urinary Tract Infections Aleksand</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>EST-135</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Rf76e86bc31</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>doi:10.3389/fmed.2020.00342</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>PMC7410981</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>020.00342 The Potential Innovative Use of ® Bacteriophages Within the DAC Hydrogel to Treat</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debr</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>EST-140</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>R36411565f8</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>pmid:30661974; doi:10.1016/j.healun.2019.01.001</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>EST-146</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>R3405f1429d</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>pmid:37279523; doi:10.1093/cid/ciad335</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>PMC10573729</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>R ARTICLE A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized P</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Characteristics, and Clinical Outc</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>doi:10.3390/antibiotics14010087</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>PMC11759190</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>nication The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages M</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>EST-157</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>R18831247ea</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>pmid:38233034; doi:10.1002/central/cn-02654937/full</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>EST-164</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>R3ec3a782bb</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>pmid:31548497; doi:10.3390/v11100891</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.mdpi.com/1999-4915/11/10/891/pdf?version=1569316224</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>INTRODUCCION Y RESULTADOS</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Proto</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>EST-165</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>R9b7fc7c6a6</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>pmid:31752578; doi:10.1177/1534734619881076</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>INTRODUCCION</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>EST-167</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Re6084b7743</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>pmid:34985344; doi:10.1177/15347346211072779</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>EST-169</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Rd7ea09ed5c</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>pmid:39074617; doi:10.1016/j.virusres.2024.199442</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>PMC11341935</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>virusres Safety and tolerability of bronchoscopic and nebulised administration of bact</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>EST-170</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Rc513775cd3</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.avsurg.2024.100302</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.avsurg.2024.100302</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>te/avsurg Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aor</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>EST-184</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>R419c6f6d67</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jdcr.2026.06.010</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>título localizado en el texto leído</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>ND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>MATERILAES Y METODOS</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
           <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>EST-188</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>R95ed8fa775</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>resumen de congreso</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>doi:10.1002/central/cn-02203985/full</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>sin texto</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>informe único</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>el estudio tiene un solo informe; no hay otra procedencia posible</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K95"/>
+  <autoFilter ref="A1:K74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -685,7 +685,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>De qué informe salió cada brazo extraído y con qué prueba se estableció el vínculo («informe único» o «título localizado en el texto leído»); «Evidencia» guarda la frase que lo demuestra. Lo establece el canal (build_brazo_informe.py), que no afirma de qué página sale cada casilla: eso es «¿Dónde viste estos datos?», el texto libre de la extracción, recortado.</t>
         </is>
       </c>
     </row>
@@ -514,176 +521,187 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sección 2.6. Dónde mirar para comprobar cualquier dato de cualquier brazo (PRISMA 2020, ítem 10a).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>73 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: arm_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: record_id</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>tipo_informe</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Tipo de informe</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: tipo_informe</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>identificadores</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Identificadores (PMID, DOI, NCT)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: identificadores</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>informes_del_estudio</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Informes del estudio</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: informes_del_estudio</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>documento_leido</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Documento leído</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: documento_leido</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Cómo se localizó</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Cómo se estableció el vínculo</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: via</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: evidencia</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>cita_de_extraccion</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>¿Dónde viste estos datos?</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: cita_de_extraccion</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>titulo_del_informe</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Título del informe</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo_del_informe</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -713,63 +731,63 @@
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="46" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>tipo_informe</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>identificadores</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>informes_del_estudio</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>documento_leido</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>Cómo se localizó</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Tipo de informe</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Identificadores (PMID, DOI, NCT)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Informes del estudio</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Documento leído</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Cómo se estableció el vínculo</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>cita_de_extraccion</t>
-        </is>
-      </c>
-      <c r="K1" s="8" t="inlineStr">
-        <is>
-          <t>titulo_del_informe</t>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>¿Dónde viste estos datos?</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Título del informe</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
+++ b/verificables revisión sistemática/S20_de_que_informe_salio_cada_brazo.xlsx
@@ -703,7 +703,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
